--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/post DFS_HRM-2031-0360/Panel-28/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/post DFS_HRM-2031-0360/Panel-28/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,19 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.73169</v>
+        <v>16.87672</v>
       </c>
       <c r="D2" t="n">
-        <v>16.62707</v>
+        <v>16.43708</v>
       </c>
       <c r="E2" t="n">
-        <v>16.7926</v>
+        <v>16.77378</v>
+      </c>
+      <c r="F2" t="n">
+        <v>42.60482</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05008</v>
+        <v>0.05092</v>
       </c>
       <c r="H2" t="n">
-        <v>1.84691</v>
+        <v>1.84136</v>
       </c>
     </row>
     <row r="3">
@@ -482,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.26777</v>
+        <v>16.83396</v>
       </c>
       <c r="D3" t="n">
-        <v>16.56197</v>
+        <v>16.39784</v>
       </c>
       <c r="E3" t="n">
-        <v>16.69937</v>
+        <v>16.62269</v>
       </c>
       <c r="F3" t="n">
-        <v>41.93966</v>
+        <v>42.38583</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.05063</v>
       </c>
       <c r="H3" t="n">
-        <v>1.81954</v>
+        <v>1.76337</v>
       </c>
     </row>
     <row r="4">
@@ -506,25 +509,23 @@
           <t>Unit 9</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+      <c r="C4" t="n">
+        <v>16.82648</v>
       </c>
       <c r="D4" t="n">
-        <v>16.35226</v>
+        <v>16.56148</v>
       </c>
       <c r="E4" t="n">
-        <v>16.78288</v>
+        <v>16.66275</v>
       </c>
       <c r="F4" t="n">
-        <v>42.0032</v>
+        <v>42.66499</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05113</v>
+        <v>0.05045</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82997</v>
+        <v>1.82726</v>
       </c>
     </row>
     <row r="5">
@@ -533,25 +534,23 @@
           <t>Unit 4</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>12,5</t>
-        </is>
+      <c r="C5" t="n">
+        <v>16.90084</v>
       </c>
       <c r="D5" t="n">
-        <v>16.5421</v>
+        <v>16.434</v>
       </c>
       <c r="E5" t="n">
-        <v>16.57579</v>
+        <v>16.73567</v>
       </c>
       <c r="F5" t="n">
-        <v>42.43649</v>
+        <v>43.23651</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05095</v>
+        <v>0.05044</v>
       </c>
       <c r="H5" t="n">
-        <v>1.82649</v>
+        <v>1.80659</v>
       </c>
     </row>
     <row r="6">
@@ -561,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.81562</v>
+        <v>16.89477</v>
       </c>
       <c r="D6" t="n">
-        <v>16.28296</v>
+        <v>16.86974</v>
       </c>
       <c r="E6" t="n">
-        <v>16.48258</v>
+        <v>16.88052</v>
       </c>
       <c r="F6" t="n">
-        <v>42.33171</v>
+        <v>42.45753</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05003</v>
-      </c>
-      <c r="H6" t="e">
-        <v>#DIV/0!</v>
+        <v>0.05149</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.81405</v>
       </c>
     </row>
     <row r="7">
@@ -586,24 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.02706</v>
+        <v>16.75172</v>
       </c>
       <c r="D7" t="n">
-        <v>16.77133</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 16.48 </t>
-        </is>
+        <v>16.10395</v>
+      </c>
+      <c r="E7" t="n">
+        <v>16.40331</v>
       </c>
       <c r="F7" t="n">
-        <v>42.26585</v>
+        <v>43.52782</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05096</v>
+        <v>0.0499</v>
       </c>
       <c r="H7" t="n">
-        <v>1.81071</v>
+        <v>1.84303</v>
       </c>
     </row>
     <row r="8">
@@ -613,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.72569</v>
+        <v>16.64262</v>
       </c>
       <c r="D8" t="n">
-        <v>16.61703</v>
+        <v>16.63531</v>
       </c>
       <c r="E8" t="n">
-        <v>16.63832</v>
+        <v>16.63666</v>
       </c>
       <c r="F8" t="n">
-        <v>42.21901</v>
+        <v>43.25312</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0495</v>
+        <v>0.05034</v>
       </c>
       <c r="H8" t="n">
-        <v>1.83022</v>
+        <v>1.82084</v>
       </c>
     </row>
     <row r="9">
@@ -638,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.84695</v>
+        <v>16.60493</v>
       </c>
       <c r="D9" t="n">
-        <v>16.63626</v>
+        <v>16.20837</v>
       </c>
       <c r="E9" t="n">
-        <v>16.60598</v>
+        <v>16.59668</v>
       </c>
       <c r="F9" t="n">
-        <v>41.4776</v>
+        <v>43.27429</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05044</v>
+        <v>0.05091</v>
       </c>
       <c r="H9" t="n">
-        <v>1.80026</v>
+        <v>1.81813</v>
       </c>
     </row>
     <row r="10">
@@ -663,482 +660,712 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.50254</v>
+        <v>17.05918</v>
       </c>
       <c r="D10" t="n">
-        <v>16.5505</v>
+        <v>16.16636</v>
       </c>
       <c r="E10" t="n">
-        <v>16.67153</v>
+        <v>16.63975</v>
       </c>
       <c r="F10" t="n">
-        <v>42.56055</v>
+        <v>41.68628</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0503</v>
+        <v>0.05028</v>
       </c>
       <c r="H10" t="n">
-        <v>1.77779</v>
+        <v>1.81362</v>
       </c>
     </row>
     <row r="11">
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pad 2</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>16.84435</v>
+      </c>
+      <c r="D11" t="n">
+        <v>16.78979</v>
+      </c>
+      <c r="E11" t="n">
+        <v>16.83261</v>
+      </c>
+      <c r="F11" t="n">
+        <v>42.14853</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.05176</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.82012</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>via 1</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>16.89019</v>
       </c>
       <c r="D12" t="n">
-        <v>1.10582</v>
+        <v>16.39595</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.74509</v>
+      </c>
+      <c r="F12" t="n">
+        <v>42.35942</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.05135</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.83814</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>16.76903</v>
       </c>
       <c r="D13" t="n">
-        <v>1.10422</v>
+        <v>16.75558</v>
+      </c>
+      <c r="E13" t="n">
+        <v>16.76051</v>
+      </c>
+      <c r="F13" t="n">
+        <v>42.06388</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.05078</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.82148</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>16.91478</v>
       </c>
       <c r="D14" t="n">
-        <v>1.10548</v>
+        <v>16.55334</v>
+      </c>
+      <c r="E14" t="n">
+        <v>16.84672</v>
+      </c>
+      <c r="F14" t="n">
+        <v>43.04913</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.05141</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.86511</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>17.10642</v>
       </c>
       <c r="D15" t="n">
-        <v>1.10257</v>
+        <v>16.67918</v>
+      </c>
+      <c r="E15" t="n">
+        <v>17.03516</v>
+      </c>
+      <c r="F15" t="n">
+        <v>41.92548</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.05092</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.84428</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>16.746</v>
       </c>
       <c r="D16" t="n">
-        <v>1.09053</v>
+        <v>16.56239</v>
+      </c>
+      <c r="E16" t="n">
+        <v>16.61954</v>
+      </c>
+      <c r="F16" t="n">
+        <v>42.69034</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.05001</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.79264</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>16.9817</v>
       </c>
       <c r="D17" t="n">
-        <v>1.10061</v>
+        <v>16.36435</v>
+      </c>
+      <c r="E17" t="n">
+        <v>16.43064</v>
+      </c>
+      <c r="F17" t="n">
+        <v>41.89979</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.04938</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.83207</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>16.89231</v>
       </c>
       <c r="D18" t="n">
-        <v>1.11514</v>
+        <v>16.29067</v>
+      </c>
+      <c r="E18" t="n">
+        <v>16.70346</v>
+      </c>
+      <c r="F18" t="n">
+        <v>41.7655</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.05131</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.84422</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>16.754</v>
       </c>
       <c r="D19" t="n">
-        <v>1.12164</v>
+        <v>16.56648</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16.73262</v>
+      </c>
+      <c r="F19" t="n">
+        <v>42.33218</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.0497</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.82176</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1.11754</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Rz mean</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Rz min</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Ra max</t>
-        </is>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>via 1</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.60651</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.1104</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>roughness</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.7403999999999999</v>
+        <v>0.60964</v>
       </c>
       <c r="D22" t="n">
-        <v>0.08108</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.60573</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.94774</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.10966</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.00768</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.09193</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.12922</v>
+        <v>1.1024</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.75454</v>
+        <v>0.59906</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08094</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.59995</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.95577</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.10941</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.00768</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.0941</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.12665</v>
+        <v>1.11384</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.75529</v>
+        <v>0.59892</v>
       </c>
       <c r="D24" t="n">
-        <v>0.08107</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.61219</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.96294</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.10904</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.00756</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.093</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.12456</v>
+        <v>1.10846</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.75685</v>
+        <v>0.60787</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0822</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.60981</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.9648</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.1063</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.00757</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.09442</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.1269</v>
+        <v>1.13168</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.74044</v>
+        <v>0.6196700000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.59937</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.94563</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.11002</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.00777</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.09218</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.12662</v>
+        <v>1.09761</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.75547</v>
+        <v>0.61628</v>
       </c>
       <c r="D27" t="n">
-        <v>0.08105</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.60376</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.97422</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.10773</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.00767</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.09454</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.12673</v>
+        <v>1.11709</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.74834</v>
+        <v>0.60215</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08055</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.59807</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.96649</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.10958</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.00762</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.09246</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.12448</v>
+        <v>1.11809</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.62236</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1.11395</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.76129</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.08327</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.61419</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.95728</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.10861</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.00762</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.09384000000000001</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.12829</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.74641</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.08173999999999999</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.60922</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.9625</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.10872</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.00753</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.09266000000000001</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.12887</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.74169</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.07883</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.6039</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.95063</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.10795</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.00756</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.09098000000000001</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.12834</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.75742</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.07955</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.61673</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.94413</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.10905</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.00756</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.09486</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.12767</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.76803</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.08112</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.61387</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.95748</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.10945</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.00764</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.09387</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.12694</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7505500000000001</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.08207</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.58917</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.93725</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.10865</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.00772</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.09431</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.12413</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.74288</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.07945000000000001</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.61183</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.9518799999999999</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.1112</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.00754</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.09499</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.12714</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>Unit 2</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>0.7603</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.08028</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.61573</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.9728</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.1075</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.00756</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.09252000000000001</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.12679</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="C38" t="n">
+        <v>0.75141</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.08137</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.60505</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.97587</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.00759</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.09222</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.12285</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>0.7607</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.08173</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.60349</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.9656</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.10851</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.00744</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.09402000000000001</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.12497</v>
+      <c r="C39" t="n">
+        <v>0.73919</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.08123</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.60479</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.94952</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.11041</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.00777</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.09334000000000001</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.12476</v>
       </c>
     </row>
   </sheetData>
